--- a/downloads/exercises/intermedio-m03-m03-l04-practice-01.xlsx
+++ b/downloads/exercises/intermedio-m03-m03-l04-practice-01.xlsx
@@ -435,7 +435,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="4" t="str">
-        <x:v>2. Multiplica el resultado por 2 para comprobar que ya es numérico.</x:v>
+        <x:v>2. Multiplica el resultado por 2 para utilizar el valor convertido en un cálculo.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
